--- a/outputs/43213.xlsx
+++ b/outputs/43213.xlsx
@@ -127,7 +127,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -326,7 +326,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="39"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -338,103 +338,103 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="B5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="B6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="n">
         <v>139.166</v>
       </c>
       <c r="B7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
         <v>168.635</v>
       </c>
       <c r="B8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>193.833</v>
       </c>
       <c r="B9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>215.085</v>
       </c>
       <c r="B10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="n">
         <v>227.315</v>
       </c>
       <c r="B11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="n">
         <v>248.878</v>
       </c>
       <c r="B12" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(A11:A12),3)</f>
-        <v>238.097</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">AVERAGE($A$11:A12)</f>
+        <v>238.0965</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="n">
         <v>264.965</v>
       </c>
       <c r="B13" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(A11:A13),3)</f>
-        <v>247.053</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">AVERAGE($A$11:A13)</f>
+        <v>247.052666666667</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="n">
         <v>291.41</v>
       </c>
       <c r="B14" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(A11:A14),3)</f>
+        <f aca="false">AVERAGE($A$11:A14)</f>
         <v>258.142</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="n">
         <v>318.038</v>
       </c>
       <c r="B15" s="4" t="n">
-        <f aca="false">ROUND(AVERAGE(A11:A15),3)</f>
-        <v>270.121</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">AVERAGE($A$11:A15)</f>
+        <v>270.1212</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
     </row>
